--- a/static/example_sheets_online/Field sampling (internal).xlsx
+++ b/static/example_sheets_online/Field sampling (internal).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glj523\Documents\github repoes\upload_web_app\static\example_sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glj523\Documents\github repoes\upload_web_app\static\example_sheets_online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAB1227-3708-4AEC-9CDB-45A8E1677EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DA8277-6018-4864-8E90-DD6800C77333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
   </bookViews>
   <sheets>
     <sheet name="eDNA_Archive_sampling_(20231027" sheetId="2" r:id="rId1"/>
@@ -711,9 +711,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -751,7 +751,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -857,7 +857,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -999,7 +999,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1730,7 +1730,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/static/example_sheets_online/Field sampling (internal).xlsx
+++ b/static/example_sheets_online/Field sampling (internal).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glj523\Documents\github repoes\upload_web_app\static\example_sheets_online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DA8277-6018-4864-8E90-DD6800C77333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEBD0D2-3D20-448C-8E10-C1DCF3C0C096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="eDNA_Archive_sampling_(20231027" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">'eDNA_Archive_sampling_(20231027'!$B$1:$S$10</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">'eDNA_Archive_sampling_(20231027'!$B$1:$S$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,19 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="125">
-  <si>
-    <t>Expected column names and positions:</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Accepted format:</t>
-  </si>
-  <si>
-    <t>Required?*</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="124">
   <si>
     <t>Core</t>
   </si>
@@ -94,16 +82,7 @@
     <t>decimal degrees, max 2 digits, max 8 decimal points (-180 to 180)</t>
   </si>
   <si>
-    <t>Examples of accepted data:</t>
-  </si>
-  <si>
-    <t>*If a column is required, this means that the sheet will be rejected if there are any values missing from that column</t>
-  </si>
-  <si>
     <t>Mathematical notation: Numbers, "()", "[]" and "," (decimal allowed only if "." is used as decimal point).</t>
-  </si>
-  <si>
-    <t>Description:</t>
   </si>
   <si>
     <t>Full names seperated by comma</t>
@@ -442,6 +421,24 @@
   </si>
   <si>
     <t>&lt;measurement/observation type&gt;: &lt;measurement/observation&gt; &lt;unit (optional)&gt;</t>
+  </si>
+  <si>
+    <t>Example data 3</t>
+  </si>
+  <si>
+    <t>Example data 2</t>
+  </si>
+  <si>
+    <t>Example data 1</t>
+  </si>
+  <si>
+    <t>Accepted format</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Expected column names and positions</t>
   </si>
 </sst>
 </file>
@@ -624,7 +621,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -640,9 +637,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
@@ -1021,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B8DB45-AD95-4AEF-BE44-A884078F1D25}">
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
@@ -1076,650 +1070,601 @@
     <col min="50" max="50" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="15" customFormat="1" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:35" s="14" customFormat="1" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" s="17" customFormat="1" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="18">
+        <v>61.139899999999997</v>
+      </c>
+      <c r="H2" s="17">
+        <v>-45.534700000000001</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="N2" s="17">
+        <v>10</v>
+      </c>
+      <c r="O2" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="P2" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="17">
+        <v>10</v>
+      </c>
+      <c r="R2" s="17">
+        <v>10</v>
+      </c>
+      <c r="S2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="T2" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="U2" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="W2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y2" s="17">
+        <v>37</v>
+      </c>
+      <c r="Z2" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA2" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB2" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC2" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD2" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE2" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF2" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" s="17" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="18">
+        <v>61.139899999999997</v>
+      </c>
+      <c r="H3" s="17">
+        <v>-45.534700000000001</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="N3" s="17">
+        <v>200</v>
+      </c>
+      <c r="O3" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="P3" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" s="17">
+        <v>200</v>
+      </c>
+      <c r="R3" s="17">
+        <v>200</v>
+      </c>
+      <c r="S3" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="T3" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="V3" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="W3" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="X3" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y3" s="17">
+        <v>37</v>
+      </c>
+      <c r="Z3" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA3" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB3" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC3" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD3" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE3" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF3" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" s="17" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" s="18">
+        <v>61.139899999999997</v>
+      </c>
+      <c r="H4" s="17">
+        <v>-45.534700000000001</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="N4" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="O4" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="R4" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="S4" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="T4" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="U4" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="V4" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="W4" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="X4" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y4" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z4" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA4" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB4" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE4" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF4" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" s="6" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="O5" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="X5" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE5" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF5" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="AG5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI5" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" s="5" customFormat="1" ht="61.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="T6" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA6" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>28</v>
+      <c r="AB6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC6" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG6" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH6" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:35" s="18" customFormat="1" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" s="19">
-        <v>61.139899999999997</v>
-      </c>
-      <c r="H2" s="18">
-        <v>-45.534700000000001</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K2" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="L2" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="N2" s="18">
-        <v>10</v>
-      </c>
-      <c r="O2" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="P2" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q2" s="18">
-        <v>10</v>
-      </c>
-      <c r="R2" s="18">
-        <v>10</v>
-      </c>
-      <c r="S2" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="T2" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="U2" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="V2" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="W2" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="X2" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y2" s="18">
-        <v>37</v>
-      </c>
-      <c r="Z2" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA2" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB2" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC2" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="AD2" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE2" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF2" s="18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="G3" s="19">
-        <v>61.139899999999997</v>
-      </c>
-      <c r="H3" s="18">
-        <v>-45.534700000000001</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="L3" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="N3" s="18">
-        <v>200</v>
-      </c>
-      <c r="O3" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="P3" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q3" s="18">
-        <v>200</v>
-      </c>
-      <c r="R3" s="18">
-        <v>200</v>
-      </c>
-      <c r="S3" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="T3" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="U3" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="V3" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="W3" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="X3" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y3" s="18">
-        <v>37</v>
-      </c>
-      <c r="Z3" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA3" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB3" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC3" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="AD3" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE3" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF3" s="18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:35" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="G4" s="19">
-        <v>61.139899999999997</v>
-      </c>
-      <c r="H4" s="18">
-        <v>-45.534700000000001</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="K4" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="N4" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="O4" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="P4" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q4" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="R4" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="S4" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="T4" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="U4" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="V4" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="W4" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="X4" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y4" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z4" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA4" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB4" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC4" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="AD4" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE4" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF4" s="18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" s="6" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="O6" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="T6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="V6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="W6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="X6" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y6" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z6" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC6" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AD6" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AE6" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF6" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="AG6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="AH6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI6" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" s="5" customFormat="1" ht="61.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="S7" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="T7" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="U7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="X7" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y7" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z7" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA7" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB7" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC7" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="AD7" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF7" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="AG7" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="AH7" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="U8" s="5"/>
-      <c r="Z8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
-        <v>10</v>
-      </c>
-    </row>
+    <row r="8" spans="1:35" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:35" s="16" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G1 AA1:AB1 P1:R1" xr:uid="{BCEA9F6D-AA44-438E-A588-55D9520F3F27}">

--- a/static/example_sheets_online/Field sampling (internal).xlsx
+++ b/static/example_sheets_online/Field sampling (internal).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glj523\Documents\github repoes\upload_web_app\static\example_sheets_online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEBD0D2-3D20-448C-8E10-C1DCF3C0C096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93AD60E-0290-4E80-9CA5-E977BAB486C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="125">
   <si>
     <t>Core</t>
   </si>
@@ -439,6 +439,9 @@
   </si>
   <si>
     <t>Expected column names and positions</t>
+  </si>
+  <si>
+    <t>Greenland</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1188,7 @@
         <v>23</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="E2" s="17" t="s">
         <v>89</v>
